--- a/Demo/MDA/demo_mda_9999_1_location.xlsx
+++ b/Demo/MDA/demo_mda_9999_1_location.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\MDA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\Demo\MDA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1461E11-F718-4000-BBA6-357F63C1053C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDFBD945-D0A6-4C10-8F10-F36E7B13BC72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="97">
   <si>
     <t>type</t>
   </si>
@@ -311,18 +311,6 @@
   </si>
   <si>
     <t>no</t>
-  </si>
-  <si>
-    <t>${l_state}</t>
-  </si>
-  <si>
-    <t>${l_district}</t>
-  </si>
-  <si>
-    <t>${l_location}</t>
-  </si>
-  <si>
-    <t>bind::type</t>
   </si>
   <si>
     <t>start</t>
@@ -404,7 +392,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -427,12 +415,40 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -455,14 +471,20 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -745,96 +767,96 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R13"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="28" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="47" style="4" customWidth="1"/>
-    <col min="4" max="4" width="41.25" style="4" customWidth="1"/>
+    <col min="2" max="2" width="21.875" style="4" customWidth="1"/>
+    <col min="3" max="3" width="39.25" style="4" customWidth="1"/>
+    <col min="4" max="4" width="15.25" style="4" customWidth="1"/>
     <col min="5" max="5" width="12.625" style="4" customWidth="1"/>
-    <col min="6" max="6" width="9.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.375" style="4" customWidth="1"/>
+    <col min="7" max="7" width="28.125" style="4" customWidth="1"/>
     <col min="8" max="8" width="20.375" style="4" customWidth="1"/>
     <col min="9" max="9" width="27.625" style="4" customWidth="1"/>
-    <col min="10" max="10" width="9.75" style="4" customWidth="1"/>
-    <col min="11" max="11" width="8.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="53.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.5" style="4" customWidth="1"/>
-    <col min="15" max="18" width="18" style="4" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="11" style="4"/>
+    <col min="10" max="10" width="12.5" style="4" customWidth="1"/>
+    <col min="11" max="11" width="10.75" style="4" customWidth="1"/>
+    <col min="12" max="12" width="17.5" style="4" customWidth="1"/>
+    <col min="13" max="13" width="14.5" style="4" customWidth="1"/>
+    <col min="14" max="14" width="20.625" style="4" customWidth="1"/>
+    <col min="15" max="15" width="18" style="4" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.875" style="4" customWidth="1"/>
+    <col min="17" max="17" width="20.375" style="4" customWidth="1"/>
+    <col min="18" max="16384" width="11" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:17" s="1" customFormat="1">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="15" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="N1" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="O1" s="13" t="s">
+      <c r="N1" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="P1" s="13" t="s">
+      <c r="O1" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="Q1" s="13" t="s">
+      <c r="P1" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="R1" s="13" t="s">
+      <c r="Q1" s="16" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="26.25">
+    <row r="2" spans="1:17" ht="26.25">
       <c r="A2" s="9" t="s">
         <v>72</v>
       </c>
       <c r="B2" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="D2" s="14"/>
+      <c r="D2" s="12"/>
       <c r="E2" s="9"/>
       <c r="F2" s="9"/>
-      <c r="G2" s="14"/>
+      <c r="G2" s="12"/>
       <c r="H2" s="9"/>
       <c r="I2" s="9"/>
       <c r="J2" s="9" t="s">
@@ -843,28 +865,27 @@
       <c r="K2" s="9"/>
       <c r="L2" s="9"/>
       <c r="M2" s="9"/>
-      <c r="N2" s="9"/>
-      <c r="O2" s="15" t="s">
+      <c r="N2" s="13" t="s">
         <v>25</v>
       </c>
+      <c r="O2" s="9"/>
       <c r="P2" s="9"/>
       <c r="Q2" s="9"/>
-      <c r="R2" s="9"/>
-    </row>
-    <row r="3" spans="1:18" ht="26.25">
+    </row>
+    <row r="3" spans="1:17" ht="26.25">
       <c r="A3" s="9" t="s">
         <v>73</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="14"/>
+      <c r="D3" s="12"/>
       <c r="E3" s="9"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="14"/>
+      <c r="G3" s="12"/>
       <c r="H3" s="9"/>
       <c r="I3" s="9"/>
       <c r="J3" s="9" t="s">
@@ -876,29 +897,26 @@
       </c>
       <c r="M3" s="9"/>
       <c r="N3" s="9"/>
-      <c r="O3" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="P3" s="15" t="s">
+      <c r="O3" s="13" t="s">
         <v>25</v>
       </c>
+      <c r="P3" s="9"/>
       <c r="Q3" s="9"/>
-      <c r="R3" s="9"/>
-    </row>
-    <row r="4" spans="1:18" ht="26.25">
+    </row>
+    <row r="4" spans="1:17" ht="26.25">
       <c r="A4" s="9" t="s">
         <v>13</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="D4" s="14"/>
+      <c r="D4" s="12"/>
       <c r="E4" s="9"/>
       <c r="F4" s="9"/>
-      <c r="G4" s="14"/>
+      <c r="G4" s="12"/>
       <c r="H4" s="9"/>
       <c r="I4" s="9"/>
       <c r="J4" s="9" t="s">
@@ -909,24 +927,23 @@
       <c r="M4" s="9"/>
       <c r="N4" s="9"/>
       <c r="O4" s="9"/>
-      <c r="P4" s="9"/>
-      <c r="Q4" s="15"/>
-      <c r="R4" s="9"/>
-    </row>
-    <row r="5" spans="1:18" ht="26.25">
+      <c r="P4" s="13"/>
+      <c r="Q4" s="9"/>
+    </row>
+    <row r="5" spans="1:17" ht="26.25">
       <c r="A5" s="9" t="s">
         <v>13</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="D5" s="14"/>
+      <c r="D5" s="12"/>
       <c r="E5" s="9"/>
       <c r="F5" s="9"/>
-      <c r="G5" s="14"/>
+      <c r="G5" s="12"/>
       <c r="H5" s="9"/>
       <c r="I5" s="9"/>
       <c r="J5" s="9" t="s">
@@ -937,28 +954,25 @@
       <c r="M5" s="9"/>
       <c r="N5" s="9"/>
       <c r="O5" s="9"/>
-      <c r="P5" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="Q5" s="15" t="s">
+      <c r="P5" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="R5" s="9"/>
-    </row>
-    <row r="6" spans="1:18" ht="26.25">
+      <c r="Q5" s="9"/>
+    </row>
+    <row r="6" spans="1:17" ht="26.25">
       <c r="A6" s="9" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="D6" s="14"/>
+      <c r="D6" s="12"/>
       <c r="E6" s="9"/>
       <c r="F6" s="9"/>
-      <c r="G6" s="14"/>
+      <c r="G6" s="12"/>
       <c r="H6" s="9"/>
       <c r="I6" s="9"/>
       <c r="J6" s="9" t="s">
@@ -970,27 +984,24 @@
       <c r="N6" s="9"/>
       <c r="O6" s="9"/>
       <c r="P6" s="9"/>
-      <c r="Q6" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="R6" s="15" t="s">
+      <c r="Q6" s="13" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:18">
+    <row r="7" spans="1:17">
       <c r="A7" s="9" t="s">
         <v>83</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="14"/>
+      <c r="D7" s="12"/>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
-      <c r="G7" s="14"/>
+      <c r="G7" s="12"/>
       <c r="H7" s="9"/>
       <c r="I7" s="9"/>
       <c r="J7" s="9" t="s">
@@ -1003,24 +1014,23 @@
       <c r="O7" s="9"/>
       <c r="P7" s="9"/>
       <c r="Q7" s="9"/>
-      <c r="R7" s="9"/>
-    </row>
-    <row r="8" spans="1:18">
+    </row>
+    <row r="8" spans="1:17">
       <c r="A8" s="9" t="s">
         <v>83</v>
       </c>
       <c r="B8" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="C8" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="14"/>
+      <c r="D8" s="12"/>
       <c r="E8" s="9"/>
       <c r="F8" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="G8" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="G8" s="12" t="s">
         <v>86</v>
       </c>
       <c r="H8" s="9"/>
@@ -1035,24 +1045,23 @@
       <c r="O8" s="9"/>
       <c r="P8" s="9"/>
       <c r="Q8" s="9"/>
-      <c r="R8" s="9"/>
-    </row>
-    <row r="9" spans="1:18">
+    </row>
+    <row r="9" spans="1:17">
       <c r="A9" s="9" t="s">
         <v>14</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="14"/>
+      <c r="D9" s="12"/>
       <c r="E9" s="9" t="s">
         <v>88</v>
       </c>
       <c r="F9" s="9"/>
-      <c r="G9" s="14"/>
+      <c r="G9" s="12"/>
       <c r="H9" s="9"/>
       <c r="I9" s="9"/>
       <c r="J9" s="9" t="s">
@@ -1065,22 +1074,21 @@
       <c r="O9" s="9"/>
       <c r="P9" s="9"/>
       <c r="Q9" s="9"/>
-      <c r="R9" s="9"/>
-    </row>
-    <row r="10" spans="1:18">
+    </row>
+    <row r="10" spans="1:17">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
       <c r="B10" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="D10" s="14"/>
+      <c r="D10" s="12"/>
       <c r="E10" s="9"/>
       <c r="F10" s="9"/>
-      <c r="G10" s="14"/>
+      <c r="G10" s="12"/>
       <c r="H10" s="9"/>
       <c r="I10" s="9"/>
       <c r="J10" s="9" t="s">
@@ -1093,22 +1101,21 @@
       <c r="O10" s="9"/>
       <c r="P10" s="9"/>
       <c r="Q10" s="9"/>
-      <c r="R10" s="9"/>
-    </row>
-    <row r="11" spans="1:18">
+    </row>
+    <row r="11" spans="1:17">
       <c r="A11" s="9" t="s">
         <v>15</v>
       </c>
       <c r="B11" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C11" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="14"/>
+      <c r="D11" s="12"/>
       <c r="E11" s="9"/>
       <c r="F11" s="9"/>
-      <c r="G11" s="14"/>
+      <c r="G11" s="12"/>
       <c r="H11" s="9"/>
       <c r="I11" s="9"/>
       <c r="J11" s="9" t="s">
@@ -1117,26 +1124,23 @@
       <c r="K11" s="9"/>
       <c r="L11" s="9"/>
       <c r="M11" s="9"/>
-      <c r="N11" s="9" t="s">
-        <v>15</v>
-      </c>
+      <c r="N11" s="9"/>
       <c r="O11" s="9"/>
       <c r="P11" s="9"/>
       <c r="Q11" s="9"/>
-      <c r="R11" s="9"/>
-    </row>
-    <row r="12" spans="1:18">
+    </row>
+    <row r="12" spans="1:17">
       <c r="A12" s="9" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
+        <v>95</v>
+      </c>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
       <c r="E12" s="9"/>
       <c r="F12" s="9"/>
-      <c r="G12" s="14"/>
+      <c r="G12" s="12"/>
       <c r="H12" s="9"/>
       <c r="I12" s="9"/>
       <c r="J12" s="9"/>
@@ -1147,20 +1151,19 @@
       <c r="O12" s="9"/>
       <c r="P12" s="9"/>
       <c r="Q12" s="9"/>
-      <c r="R12" s="9"/>
-    </row>
-    <row r="13" spans="1:18">
+    </row>
+    <row r="13" spans="1:17">
       <c r="A13" s="9" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
+        <v>94</v>
+      </c>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
       <c r="E13" s="9"/>
       <c r="F13" s="9"/>
-      <c r="G13" s="14"/>
+      <c r="G13" s="12"/>
       <c r="H13" s="9"/>
       <c r="I13" s="9"/>
       <c r="J13" s="9"/>
@@ -1171,7 +1174,6 @@
       <c r="O13" s="9"/>
       <c r="P13" s="9"/>
       <c r="Q13" s="9"/>
-      <c r="R13" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Demo/MDA/demo_mda_9999_1_location.xlsx
+++ b/Demo/MDA/demo_mda_9999_1_location.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\Demo\MDA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDFBD945-D0A6-4C10-8F10-F36E7B13BC72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E120B472-3A85-4198-A4FD-B1CB12F32477}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="171">
   <si>
     <t>type</t>
   </si>
@@ -121,18 +121,9 @@
     <t>read_only</t>
   </si>
   <si>
-    <t>demo_mda_9999_1_location</t>
-  </si>
-  <si>
-    <t>(Demo) 1. MDA Location Form</t>
-  </si>
-  <si>
     <t>Enter the total population of the village</t>
   </si>
   <si>
-    <t>Enter the eligible population of the village</t>
-  </si>
-  <si>
     <t>GPS of the village</t>
   </si>
   <si>
@@ -148,108 +139,9 @@
     <t>Select District / LGA / County</t>
   </si>
   <si>
-    <t>Kongo Central</t>
-  </si>
-  <si>
-    <t>Sahel Heights</t>
-  </si>
-  <si>
-    <t>Zambezi Plateau</t>
-  </si>
-  <si>
     <t>state</t>
   </si>
   <si>
-    <t>Bacongo</t>
-  </si>
-  <si>
-    <t>Djiri</t>
-  </si>
-  <si>
-    <t>Kintélé</t>
-  </si>
-  <si>
-    <t>Madibou</t>
-  </si>
-  <si>
-    <t>Makélékélé</t>
-  </si>
-  <si>
-    <t>Mfilou</t>
-  </si>
-  <si>
-    <t>Moungali</t>
-  </si>
-  <si>
-    <t>Ouenzé</t>
-  </si>
-  <si>
-    <t>Poto-Poto</t>
-  </si>
-  <si>
-    <t>Talangaï</t>
-  </si>
-  <si>
-    <t>Agadez South</t>
-  </si>
-  <si>
-    <t>Bamako North</t>
-  </si>
-  <si>
-    <t>Bandiagara</t>
-  </si>
-  <si>
-    <t>Dogon Plateau</t>
-  </si>
-  <si>
-    <t>Gao Central</t>
-  </si>
-  <si>
-    <t>Joliba</t>
-  </si>
-  <si>
-    <t>Kayes</t>
-  </si>
-  <si>
-    <t>Mopti Riverside</t>
-  </si>
-  <si>
-    <t>Segou</t>
-  </si>
-  <si>
-    <t>Timbuktu West</t>
-  </si>
-  <si>
-    <t>Baobab Valley</t>
-  </si>
-  <si>
-    <t>Copperbelt</t>
-  </si>
-  <si>
-    <t>High Veldt</t>
-  </si>
-  <si>
-    <t>Kafue</t>
-  </si>
-  <si>
-    <t>Kariba</t>
-  </si>
-  <si>
-    <t>Limpopo East</t>
-  </si>
-  <si>
-    <t>Luangwa</t>
-  </si>
-  <si>
-    <t>Manyara</t>
-  </si>
-  <si>
-    <t>Okavango North</t>
-  </si>
-  <si>
-    <t>Savanna Ridge</t>
-  </si>
-  <si>
     <t>district</t>
   </si>
   <si>
@@ -295,9 +187,6 @@
     <t>l_eligible_pop</t>
   </si>
   <si>
-    <t>The eligible population cannot exceed the total population</t>
-  </si>
-  <si>
     <t>l_gps</t>
   </si>
   <si>
@@ -325,14 +214,347 @@
     <t>l_start</t>
   </si>
   <si>
-    <t>. &lt;= ${l_total_pop}</t>
+    <t>Bandundu</t>
+  </si>
+  <si>
+    <t>Bas-Congo</t>
+  </si>
+  <si>
+    <t>Haut-Katanga</t>
+  </si>
+  <si>
+    <t>Ituri</t>
+  </si>
+  <si>
+    <t>Kasai-Central</t>
+  </si>
+  <si>
+    <t>Kasai-Oriental</t>
+  </si>
+  <si>
+    <t>Kwango</t>
+  </si>
+  <si>
+    <t>Lualaba</t>
+  </si>
+  <si>
+    <t>Nord-Kivu</t>
+  </si>
+  <si>
+    <t>Sud-Kivu</t>
+  </si>
+  <si>
+    <t>Bagata</t>
+  </si>
+  <si>
+    <t>Bulungu</t>
+  </si>
+  <si>
+    <t>Boma</t>
+  </si>
+  <si>
+    <t>Matadi</t>
+  </si>
+  <si>
+    <t>Kambove</t>
+  </si>
+  <si>
+    <t>Kipushi</t>
+  </si>
+  <si>
+    <t>Bunia</t>
+  </si>
+  <si>
+    <t>Mambasa</t>
+  </si>
+  <si>
+    <t>Dibaya</t>
+  </si>
+  <si>
+    <t>Kazumba</t>
+  </si>
+  <si>
+    <t>Lupatapata</t>
+  </si>
+  <si>
+    <t>Miabi</t>
+  </si>
+  <si>
+    <t>Kenge</t>
+  </si>
+  <si>
+    <t>Popokabaka</t>
+  </si>
+  <si>
+    <t>Fungurume</t>
+  </si>
+  <si>
+    <t>Kolwezi</t>
+  </si>
+  <si>
+    <t>Beni</t>
+  </si>
+  <si>
+    <t>Rutshuru</t>
+  </si>
+  <si>
+    <t>Kalehe</t>
+  </si>
+  <si>
+    <t>Uvira</t>
+  </si>
+  <si>
+    <t>health_facility</t>
+  </si>
+  <si>
+    <t>Kikongo Centre</t>
+  </si>
+  <si>
+    <t>Oicha Centre</t>
+  </si>
+  <si>
+    <t>Nzadi Centre</t>
+  </si>
+  <si>
+    <t>Niadi Centre</t>
+  </si>
+  <si>
+    <t>Mudzipela Centre</t>
+  </si>
+  <si>
+    <t>Tshikapa Centre</t>
+  </si>
+  <si>
+    <t>Tenke Centre</t>
+  </si>
+  <si>
+    <t>Ihusi Centre</t>
+  </si>
+  <si>
+    <t>Kakanda Centre</t>
+  </si>
+  <si>
+    <t>Musese</t>
+  </si>
+  <si>
+    <t>Bukanga</t>
+  </si>
+  <si>
+    <t>Lumata Centre</t>
+  </si>
+  <si>
+    <t>Dilala Centre</t>
+  </si>
+  <si>
+    <t>Mulenda</t>
+  </si>
+  <si>
+    <t>Makeke Centre</t>
+  </si>
+  <si>
+    <t>Kinkanda Centre</t>
+  </si>
+  <si>
+    <t>Katende Centre</t>
+  </si>
+  <si>
+    <t>Yasa Bonga</t>
+  </si>
+  <si>
+    <t>Kiwanja Centre</t>
+  </si>
+  <si>
+    <t>Kavimvira Centre</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Misangi</t>
+  </si>
+  <si>
+    <t>Mutoshi</t>
+  </si>
+  <si>
+    <t>Nyabibwe</t>
+  </si>
+  <si>
+    <t>Mwadingusha</t>
+  </si>
+  <si>
+    <t>Kalelu</t>
+  </si>
+  <si>
+    <t>Sange</t>
+  </si>
+  <si>
+    <t>Kimputu</t>
+  </si>
+  <si>
+    <t>Soyo</t>
+  </si>
+  <si>
+    <t>Bwito</t>
+  </si>
+  <si>
+    <t>Kafubu</t>
+  </si>
+  <si>
+    <t>Biakato</t>
+  </si>
+  <si>
+    <t>Hoho</t>
+  </si>
+  <si>
+    <t>Mbujimayi Rural</t>
+  </si>
+  <si>
+    <t>Lubudi</t>
+  </si>
+  <si>
+    <t>Kiyaka</t>
+  </si>
+  <si>
+    <t>Lovo</t>
+  </si>
+  <si>
+    <t>Mavivi</t>
+  </si>
+  <si>
+    <t>Kando</t>
+  </si>
+  <si>
+    <t>Kabondo</t>
+  </si>
+  <si>
+    <t>Kipata</t>
+  </si>
+  <si>
+    <t>select_one health_facility</t>
+  </si>
+  <si>
+    <t>select_one location</t>
+  </si>
+  <si>
+    <t>select_one location_id</t>
+  </si>
+  <si>
+    <t>location_id</t>
+  </si>
+  <si>
+    <t>district = ${l_district}</t>
+  </si>
+  <si>
+    <t>health_facility = ${l_health_facility}</t>
+  </si>
+  <si>
+    <t>location = ${l_location}</t>
+  </si>
+  <si>
+    <t>Total number of boys aged 0-4 years eligible for treatment</t>
+  </si>
+  <si>
+    <t>Total number of girls aged 0-4 years eligible for treatment</t>
+  </si>
+  <si>
+    <t>Total number of boys aged 5-14 years eligible for treatment</t>
+  </si>
+  <si>
+    <t>Total number of girls aged 5-14 years eligible for treatment</t>
+  </si>
+  <si>
+    <t>Total number of boys aged more than 15 years eligible for treatment</t>
+  </si>
+  <si>
+    <t>Total number of girls aged more than years eligible for treatment</t>
+  </si>
+  <si>
+    <t>l_eligible_boy_0_4</t>
+  </si>
+  <si>
+    <t>l_eligible_boy_5_14</t>
+  </si>
+  <si>
+    <t>l_eligible_girl_0_4</t>
+  </si>
+  <si>
+    <t>l_eligible_girl_5_14</t>
+  </si>
+  <si>
+    <t>l_eligible_boy_15_more</t>
+  </si>
+  <si>
+    <t>l_eligible_girl_15_more</t>
+  </si>
+  <si>
+    <t>calculate</t>
+  </si>
+  <si>
+    <t>Total eligible population of the village</t>
+  </si>
+  <si>
+    <t>${l_eligible_boy_0_4} + ${l_eligible_girl_0_4} + ${l_eligible_boy_5_14} + ${l_eligible_girl_5_14} + ${l_eligible_boy_15_more} + ${l_eligible_girl_15_more}</t>
+  </si>
+  <si>
+    <t>(Demo) 1. MDA Location Form V2</t>
+  </si>
+  <si>
+    <t>demo_mda_9999_1_location_v2</t>
+  </si>
+  <si>
+    <t>l_recorder_id</t>
+  </si>
+  <si>
+    <t>recorder_id</t>
+  </si>
+  <si>
+    <t>01</t>
+  </si>
+  <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>05</t>
+  </si>
+  <si>
+    <t>06</t>
+  </si>
+  <si>
+    <t>07</t>
+  </si>
+  <si>
+    <t>08</t>
+  </si>
+  <si>
+    <t>09</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>select_one recorder_id</t>
+  </si>
+  <si>
+    <t>Select the recorder ID</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -377,6 +599,19 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -392,7 +627,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -415,40 +650,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
-      </left>
-      <right style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
-      </right>
-      <top style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -473,17 +680,35 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -767,12 +992,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="28" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.875" style="4" customWidth="1"/>
-    <col min="3" max="3" width="39.25" style="4" customWidth="1"/>
+    <col min="3" max="3" width="56.625" style="4" customWidth="1"/>
     <col min="4" max="4" width="15.25" style="4" customWidth="1"/>
     <col min="5" max="5" width="12.625" style="4" customWidth="1"/>
     <col min="6" max="6" width="13.375" style="4" customWidth="1"/>
@@ -781,7 +1006,7 @@
     <col min="9" max="9" width="27.625" style="4" customWidth="1"/>
     <col min="10" max="10" width="12.5" style="4" customWidth="1"/>
     <col min="11" max="11" width="10.75" style="4" customWidth="1"/>
-    <col min="12" max="12" width="17.5" style="4" customWidth="1"/>
+    <col min="12" max="12" width="23.375" style="4" customWidth="1"/>
     <col min="13" max="13" width="14.5" style="4" customWidth="1"/>
     <col min="14" max="14" width="20.625" style="4" customWidth="1"/>
     <col min="15" max="15" width="18" style="4" bestFit="1" customWidth="1"/>
@@ -791,96 +1016,92 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="G1" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="14" t="s">
+      <c r="K1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="15" t="s">
+      <c r="L1" s="5" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="N1" s="16" t="s">
+      <c r="N1" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="O1" s="16" t="s">
+      <c r="O1" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="P1" s="16" t="s">
+      <c r="P1" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="Q1" s="16" t="s">
+      <c r="Q1" s="21" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="26.25">
-      <c r="A2" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="C2" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="D2" s="12"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
-      <c r="N2" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="O2" s="9"/>
-      <c r="P2" s="9"/>
-      <c r="Q2" s="9"/>
+    <row r="2" spans="1:17" s="3" customFormat="1">
+      <c r="A2" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="C2" s="22" t="s">
+        <v>170</v>
+      </c>
+      <c r="D2" s="22"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="23"/>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
     </row>
     <row r="3" spans="1:17" ht="26.25">
       <c r="A3" s="9" t="s">
-        <v>73</v>
+        <v>36</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D3" s="12"/>
       <c r="E3" s="9"/>
@@ -892,26 +1113,24 @@
         <v>12</v>
       </c>
       <c r="K3" s="9"/>
-      <c r="L3" s="9" t="s">
-        <v>76</v>
-      </c>
+      <c r="L3" s="9"/>
       <c r="M3" s="9"/>
-      <c r="N3" s="9"/>
-      <c r="O3" s="13" t="s">
+      <c r="N3" s="13" t="s">
         <v>25</v>
       </c>
+      <c r="O3" s="9"/>
       <c r="P3" s="9"/>
       <c r="Q3" s="9"/>
     </row>
     <row r="4" spans="1:17" ht="26.25">
       <c r="A4" s="9" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>77</v>
+        <v>39</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>82</v>
+        <v>33</v>
       </c>
       <c r="D4" s="12"/>
       <c r="E4" s="9"/>
@@ -923,22 +1142,26 @@
         <v>12</v>
       </c>
       <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
+      <c r="L4" s="9" t="s">
+        <v>40</v>
+      </c>
       <c r="M4" s="9"/>
       <c r="N4" s="9"/>
-      <c r="O4" s="9"/>
-      <c r="P4" s="13"/>
+      <c r="O4" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="P4" s="9"/>
       <c r="Q4" s="9"/>
     </row>
     <row r="5" spans="1:17" ht="26.25">
       <c r="A5" s="9" t="s">
-        <v>13</v>
+        <v>131</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="D5" s="12"/>
       <c r="E5" s="9"/>
@@ -950,24 +1173,24 @@
         <v>12</v>
       </c>
       <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
+      <c r="L5" s="9" t="s">
+        <v>135</v>
+      </c>
       <c r="M5" s="9"/>
       <c r="N5" s="9"/>
       <c r="O5" s="9"/>
-      <c r="P5" s="13" t="s">
-        <v>25</v>
-      </c>
+      <c r="P5" s="13"/>
       <c r="Q5" s="9"/>
     </row>
-    <row r="6" spans="1:17" ht="26.25">
+    <row r="6" spans="1:17" ht="33.75">
       <c r="A6" s="9" t="s">
-        <v>13</v>
+        <v>132</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="D6" s="12"/>
       <c r="E6" s="9"/>
@@ -979,24 +1202,26 @@
         <v>12</v>
       </c>
       <c r="K6" s="9"/>
-      <c r="L6" s="9"/>
+      <c r="L6" s="14" t="s">
+        <v>136</v>
+      </c>
       <c r="M6" s="9"/>
       <c r="N6" s="9"/>
       <c r="O6" s="9"/>
-      <c r="P6" s="9"/>
-      <c r="Q6" s="13" t="s">
+      <c r="P6" s="13" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="7" spans="1:17">
+      <c r="Q6" s="9"/>
+    </row>
+    <row r="7" spans="1:17" ht="26.25">
       <c r="A7" s="9" t="s">
-        <v>83</v>
+        <v>133</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>84</v>
+        <v>43</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="D7" s="12"/>
       <c r="E7" s="9"/>
@@ -1008,31 +1233,31 @@
         <v>12</v>
       </c>
       <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
+      <c r="L7" s="9" t="s">
+        <v>137</v>
+      </c>
       <c r="M7" s="9"/>
       <c r="N7" s="9"/>
       <c r="O7" s="9"/>
       <c r="P7" s="9"/>
-      <c r="Q7" s="9"/>
+      <c r="Q7" s="13" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="8" spans="1:17">
       <c r="A8" s="9" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D8" s="12"/>
       <c r="E8" s="9"/>
-      <c r="F8" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="G8" s="12" t="s">
-        <v>86</v>
-      </c>
+      <c r="F8" s="9"/>
+      <c r="G8" s="12"/>
       <c r="H8" s="9"/>
       <c r="I8" s="9"/>
       <c r="J8" s="9" t="s">
@@ -1048,18 +1273,16 @@
     </row>
     <row r="9" spans="1:17">
       <c r="A9" s="9" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>87</v>
+        <v>144</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="D9" s="12"/>
-      <c r="E9" s="9" t="s">
-        <v>88</v>
-      </c>
+      <c r="E9" s="9"/>
       <c r="F9" s="9"/>
       <c r="G9" s="12"/>
       <c r="H9" s="9"/>
@@ -1077,13 +1300,13 @@
     </row>
     <row r="10" spans="1:17">
       <c r="A10" s="9" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>89</v>
+        <v>146</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>33</v>
+        <v>139</v>
       </c>
       <c r="D10" s="12"/>
       <c r="E10" s="9"/>
@@ -1104,13 +1327,13 @@
     </row>
     <row r="11" spans="1:17">
       <c r="A11" s="9" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>90</v>
+        <v>145</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>34</v>
+        <v>140</v>
       </c>
       <c r="D11" s="12"/>
       <c r="E11" s="9"/>
@@ -1119,7 +1342,7 @@
       <c r="H11" s="9"/>
       <c r="I11" s="9"/>
       <c r="J11" s="9" t="s">
-        <v>91</v>
+        <v>12</v>
       </c>
       <c r="K11" s="9"/>
       <c r="L11" s="9"/>
@@ -1131,19 +1354,23 @@
     </row>
     <row r="12" spans="1:17">
       <c r="A12" s="9" t="s">
-        <v>92</v>
+        <v>47</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="C12" s="12"/>
+        <v>147</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>141</v>
+      </c>
       <c r="D12" s="12"/>
       <c r="E12" s="9"/>
       <c r="F12" s="9"/>
       <c r="G12" s="12"/>
       <c r="H12" s="9"/>
       <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
+      <c r="J12" s="9" t="s">
+        <v>12</v>
+      </c>
       <c r="K12" s="9"/>
       <c r="L12" s="9"/>
       <c r="M12" s="9"/>
@@ -1154,19 +1381,23 @@
     </row>
     <row r="13" spans="1:17">
       <c r="A13" s="9" t="s">
-        <v>93</v>
+        <v>47</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="C13" s="12"/>
+        <v>148</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>142</v>
+      </c>
       <c r="D13" s="12"/>
       <c r="E13" s="9"/>
       <c r="F13" s="9"/>
       <c r="G13" s="12"/>
       <c r="H13" s="9"/>
       <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
+      <c r="J13" s="9" t="s">
+        <v>12</v>
+      </c>
       <c r="K13" s="9"/>
       <c r="L13" s="9"/>
       <c r="M13" s="9"/>
@@ -1174,6 +1405,189 @@
       <c r="O13" s="9"/>
       <c r="P13" s="9"/>
       <c r="Q13" s="9"/>
+    </row>
+    <row r="14" spans="1:17">
+      <c r="A14" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="D14" s="12"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K14" s="9"/>
+      <c r="L14" s="9"/>
+      <c r="M14" s="9"/>
+      <c r="N14" s="9"/>
+      <c r="O14" s="9"/>
+      <c r="P14" s="9"/>
+      <c r="Q14" s="9"/>
+    </row>
+    <row r="15" spans="1:17">
+      <c r="A15" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="D15" s="12"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="J15" s="9"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="9"/>
+      <c r="M15" s="9"/>
+      <c r="N15" s="9"/>
+      <c r="O15" s="9"/>
+      <c r="P15" s="9"/>
+      <c r="Q15" s="9"/>
+    </row>
+    <row r="16" spans="1:17">
+      <c r="A16" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16" s="12"/>
+      <c r="E16" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F16" s="9"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="9"/>
+      <c r="O16" s="9"/>
+      <c r="P16" s="9"/>
+      <c r="Q16" s="9"/>
+    </row>
+    <row r="17" spans="1:17">
+      <c r="A17" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" s="12"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K17" s="9"/>
+      <c r="L17" s="9"/>
+      <c r="M17" s="9"/>
+      <c r="N17" s="9"/>
+      <c r="O17" s="9"/>
+      <c r="P17" s="9"/>
+      <c r="Q17" s="9"/>
+    </row>
+    <row r="18" spans="1:17">
+      <c r="A18" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D18" s="12"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="K18" s="9"/>
+      <c r="L18" s="9"/>
+      <c r="M18" s="9"/>
+      <c r="N18" s="9"/>
+      <c r="O18" s="9"/>
+      <c r="P18" s="9"/>
+      <c r="Q18" s="9"/>
+    </row>
+    <row r="19" spans="1:17">
+      <c r="A19" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="9"/>
+      <c r="K19" s="9"/>
+      <c r="L19" s="9"/>
+      <c r="M19" s="9"/>
+      <c r="N19" s="9"/>
+      <c r="O19" s="9"/>
+      <c r="P19" s="9"/>
+      <c r="Q19" s="9"/>
+    </row>
+    <row r="20" spans="1:17">
+      <c r="A20" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="9"/>
+      <c r="K20" s="9"/>
+      <c r="L20" s="9"/>
+      <c r="M20" s="9"/>
+      <c r="N20" s="9"/>
+      <c r="O20" s="9"/>
+      <c r="P20" s="9"/>
+      <c r="Q20" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1183,15 +1597,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7372205D-7249-4602-BD04-2FE7FF6FE428}">
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:G109"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="14.375" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="20.125" customWidth="1"/>
     <col min="4" max="4" width="14.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="2" customFormat="1">
+    <row r="1" spans="1:7" s="2" customFormat="1">
       <c r="A1" s="6" t="s">
         <v>16</v>
       </c>
@@ -1202,472 +1618,1770 @@
         <v>2</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="C2" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="D2" s="10"/>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="D3" s="10"/>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="D4" s="10"/>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="10"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="10"/>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" s="4" customFormat="1">
+      <c r="A2" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+    </row>
+    <row r="3" spans="1:7" s="4" customFormat="1">
+      <c r="A3" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+    </row>
+    <row r="4" spans="1:7" s="4" customFormat="1">
+      <c r="A4" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+    </row>
+    <row r="5" spans="1:7" s="4" customFormat="1">
+      <c r="A5" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+    </row>
+    <row r="6" spans="1:7" s="4" customFormat="1">
+      <c r="A6" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+    </row>
+    <row r="7" spans="1:7" s="4" customFormat="1">
+      <c r="A7" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+    </row>
+    <row r="8" spans="1:7" s="4" customFormat="1">
+      <c r="A8" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+    </row>
+    <row r="9" spans="1:7" s="4" customFormat="1">
+      <c r="A9" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+    </row>
+    <row r="10" spans="1:7" s="4" customFormat="1">
+      <c r="A10" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+    </row>
+    <row r="11" spans="1:7" s="4" customFormat="1">
+      <c r="A11" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+    </row>
+    <row r="12" spans="1:7" s="4" customFormat="1">
+      <c r="A12" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>167</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+    </row>
+    <row r="13" spans="1:7" s="4" customFormat="1">
+      <c r="A13" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+    </row>
+    <row r="14" spans="1:7" s="4" customFormat="1">
+      <c r="A14" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="B14" s="16">
+        <v>99</v>
+      </c>
+      <c r="C14" s="17">
+        <v>99</v>
+      </c>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+    </row>
+    <row r="15" spans="1:7" s="4" customFormat="1">
+      <c r="A15" s="16"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10"/>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="10"/>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="10"/>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="D19" s="10"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="10"/>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="D20" s="10"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="10"/>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="10"/>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D22" s="10"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="10"/>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="D23" s="10"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="10"/>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="10"/>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="10"/>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="9"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="10"/>
+      <c r="G26" s="10"/>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="E27" s="10"/>
+      <c r="F27" s="10"/>
+      <c r="G27" s="10"/>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="E28" s="10"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="10"/>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="B6" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="9" t="s">
+      <c r="C29" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="B7" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="9" t="s">
+      <c r="D29" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="E29" s="10"/>
+      <c r="F29" s="10"/>
+      <c r="G29" s="10"/>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="E30" s="10"/>
+      <c r="F30" s="10"/>
+      <c r="G30" s="10"/>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B31" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="E31" s="10"/>
+      <c r="F31" s="10"/>
+      <c r="G31" s="10"/>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="E32" s="10"/>
+      <c r="F32" s="10"/>
+      <c r="G32" s="10"/>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E33" s="10"/>
+      <c r="F33" s="10"/>
+      <c r="G33" s="10"/>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="D34" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E34" s="10"/>
+      <c r="F34" s="10"/>
+      <c r="G34" s="10"/>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B35" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="E35" s="10"/>
+      <c r="F35" s="10"/>
+      <c r="G35" s="10"/>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B36" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="D36" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="E36" s="10"/>
+      <c r="F36" s="10"/>
+      <c r="G36" s="10"/>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B37" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="E37" s="10"/>
+      <c r="F37" s="10"/>
+      <c r="G37" s="10"/>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="D38" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="E38" s="10"/>
+      <c r="F38" s="10"/>
+      <c r="G38" s="10"/>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="E39" s="10"/>
+      <c r="F39" s="10"/>
+      <c r="G39" s="10"/>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B40" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D40" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="E40" s="10"/>
+      <c r="F40" s="10"/>
+      <c r="G40" s="10"/>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B41" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="D41" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="E41" s="10"/>
+      <c r="F41" s="10"/>
+      <c r="G41" s="10"/>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="D42" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="E42" s="10"/>
+      <c r="F42" s="10"/>
+      <c r="G42" s="10"/>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="C43" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="D43" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="E43" s="10"/>
+      <c r="F43" s="10"/>
+      <c r="G43" s="10"/>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B44" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="D44" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="E44" s="10"/>
+      <c r="F44" s="10"/>
+      <c r="G44" s="10"/>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="C45" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="D45" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="E45" s="10"/>
+      <c r="F45" s="10"/>
+      <c r="G45" s="10"/>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B46" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="C46" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="D46" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="E46" s="10"/>
+      <c r="F46" s="10"/>
+      <c r="G46" s="10"/>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" s="10"/>
+      <c r="B47" s="10"/>
+      <c r="C47" s="11"/>
+      <c r="D47" s="10"/>
+      <c r="E47" s="10"/>
+      <c r="F47" s="10"/>
+      <c r="G47" s="10"/>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="B48" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="C48" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D48" s="10"/>
+      <c r="E48" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="F48" s="10"/>
+      <c r="G48" s="10"/>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="B49" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="C49" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="D49" s="10"/>
+      <c r="E49" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="F49" s="10"/>
+      <c r="G49" s="10"/>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="B50" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="C50" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="D50" s="10"/>
+      <c r="E50" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="B8" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="B19" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="B20" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="B21" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D21" s="10" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="D22" s="10" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="B23" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="D23" s="10" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="B24" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="B25" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="B26" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="D26" s="10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="B27" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="D27" s="10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="B28" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="D28" s="10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="B29" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="D29" s="10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="B30" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="D30" s="10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="B31" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="C31" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D31" s="10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="B32" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="D32" s="10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="B33" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="C33" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="D33" s="10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4">
-      <c r="A34" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="B34" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="C34" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="D34" s="10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="A35" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="B35" s="10" t="s">
+      <c r="F50" s="10"/>
+      <c r="G50" s="10"/>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="B51" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="C51" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="D51" s="10"/>
+      <c r="E51" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="C35" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D35" s="10" t="s">
-        <v>39</v>
+      <c r="F51" s="10"/>
+      <c r="G51" s="10"/>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="B52" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="C52" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="D52" s="10"/>
+      <c r="E52" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="F52" s="10"/>
+      <c r="G52" s="10"/>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="B53" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="C53" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="D53" s="10"/>
+      <c r="E53" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="F53" s="10"/>
+      <c r="G53" s="10"/>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="B54" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="C54" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="D54" s="10"/>
+      <c r="E54" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="F54" s="10"/>
+      <c r="G54" s="10"/>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="B55" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="C55" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="D55" s="10"/>
+      <c r="E55" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="F55" s="10"/>
+      <c r="G55" s="10"/>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="B56" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="C56" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="D56" s="10"/>
+      <c r="E56" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="F56" s="10"/>
+      <c r="G56" s="10"/>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="B57" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="C57" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="D57" s="10"/>
+      <c r="E57" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="F57" s="10"/>
+      <c r="G57" s="10"/>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="B58" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="C58" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="D58" s="10"/>
+      <c r="E58" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="F58" s="10"/>
+      <c r="G58" s="10"/>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="B59" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="C59" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="D59" s="10"/>
+      <c r="E59" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="F59" s="10"/>
+      <c r="G59" s="10"/>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="B60" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="C60" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="D60" s="10"/>
+      <c r="E60" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="F60" s="10"/>
+      <c r="G60" s="10"/>
+    </row>
+    <row r="61" spans="1:7">
+      <c r="A61" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="B61" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="C61" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="D61" s="10"/>
+      <c r="E61" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="F61" s="10"/>
+      <c r="G61" s="10"/>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="B62" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="C62" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="D62" s="10"/>
+      <c r="E62" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="F62" s="10"/>
+      <c r="G62" s="10"/>
+    </row>
+    <row r="63" spans="1:7">
+      <c r="A63" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="B63" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="C63" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="D63" s="10"/>
+      <c r="E63" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="F63" s="10"/>
+      <c r="G63" s="10"/>
+    </row>
+    <row r="64" spans="1:7">
+      <c r="A64" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="B64" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="C64" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="D64" s="10"/>
+      <c r="E64" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="F64" s="10"/>
+      <c r="G64" s="10"/>
+    </row>
+    <row r="65" spans="1:7">
+      <c r="A65" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="B65" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="C65" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="D65" s="10"/>
+      <c r="E65" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="F65" s="10"/>
+      <c r="G65" s="10"/>
+    </row>
+    <row r="66" spans="1:7">
+      <c r="A66" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="B66" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="C66" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="D66" s="10"/>
+      <c r="E66" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="F66" s="10"/>
+      <c r="G66" s="10"/>
+    </row>
+    <row r="67" spans="1:7">
+      <c r="A67" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="B67" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="C67" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="D67" s="10"/>
+      <c r="E67" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="F67" s="10"/>
+      <c r="G67" s="10"/>
+    </row>
+    <row r="68" spans="1:7">
+      <c r="A68" s="10"/>
+      <c r="B68" s="10"/>
+      <c r="C68" s="11"/>
+      <c r="D68" s="10"/>
+      <c r="E68" s="10"/>
+      <c r="F68" s="10"/>
+      <c r="G68" s="10"/>
+    </row>
+    <row r="69" spans="1:7">
+      <c r="A69" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="B69" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="C69" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="D69" s="10"/>
+      <c r="E69" s="10"/>
+      <c r="F69" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="G69" s="10"/>
+    </row>
+    <row r="70" spans="1:7">
+      <c r="A70" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="B70" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="C70" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="D70" s="10"/>
+      <c r="E70" s="10"/>
+      <c r="F70" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="G70" s="10"/>
+    </row>
+    <row r="71" spans="1:7">
+      <c r="A71" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="B71" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="C71" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="D71" s="10"/>
+      <c r="E71" s="10"/>
+      <c r="F71" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="G71" s="10"/>
+    </row>
+    <row r="72" spans="1:7">
+      <c r="A72" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="B72" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="C72" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="D72" s="10"/>
+      <c r="E72" s="10"/>
+      <c r="F72" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="G72" s="10"/>
+    </row>
+    <row r="73" spans="1:7">
+      <c r="A73" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="B73" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="C73" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="D73" s="10"/>
+      <c r="E73" s="10"/>
+      <c r="F73" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="G73" s="10"/>
+    </row>
+    <row r="74" spans="1:7">
+      <c r="A74" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="B74" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="C74" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="D74" s="10"/>
+      <c r="E74" s="10"/>
+      <c r="F74" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="G74" s="10"/>
+    </row>
+    <row r="75" spans="1:7">
+      <c r="A75" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="B75" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="C75" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="D75" s="10"/>
+      <c r="E75" s="10"/>
+      <c r="F75" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="G75" s="10"/>
+    </row>
+    <row r="76" spans="1:7">
+      <c r="A76" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="B76" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="C76" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="D76" s="10"/>
+      <c r="E76" s="10"/>
+      <c r="F76" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="G76" s="10"/>
+    </row>
+    <row r="77" spans="1:7">
+      <c r="A77" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="B77" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="C77" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="D77" s="10"/>
+      <c r="E77" s="10"/>
+      <c r="F77" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="G77" s="10"/>
+    </row>
+    <row r="78" spans="1:7">
+      <c r="A78" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="B78" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="C78" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="D78" s="10"/>
+      <c r="E78" s="10"/>
+      <c r="F78" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="G78" s="10"/>
+    </row>
+    <row r="79" spans="1:7">
+      <c r="A79" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="B79" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="C79" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="D79" s="10"/>
+      <c r="E79" s="10"/>
+      <c r="F79" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="G79" s="10"/>
+    </row>
+    <row r="80" spans="1:7">
+      <c r="A80" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="B80" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="C80" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="D80" s="10"/>
+      <c r="E80" s="10"/>
+      <c r="F80" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="G80" s="10"/>
+    </row>
+    <row r="81" spans="1:7">
+      <c r="A81" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="B81" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="C81" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="D81" s="10"/>
+      <c r="E81" s="10"/>
+      <c r="F81" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="G81" s="10"/>
+    </row>
+    <row r="82" spans="1:7">
+      <c r="A82" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="B82" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="C82" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="D82" s="10"/>
+      <c r="E82" s="10"/>
+      <c r="F82" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="G82" s="10"/>
+    </row>
+    <row r="83" spans="1:7">
+      <c r="A83" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="B83" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="C83" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="D83" s="10"/>
+      <c r="E83" s="10"/>
+      <c r="F83" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="G83" s="10"/>
+    </row>
+    <row r="84" spans="1:7">
+      <c r="A84" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="B84" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="C84" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="D84" s="10"/>
+      <c r="E84" s="10"/>
+      <c r="F84" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="G84" s="10"/>
+    </row>
+    <row r="85" spans="1:7">
+      <c r="A85" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="B85" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="C85" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="D85" s="10"/>
+      <c r="E85" s="10"/>
+      <c r="F85" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="G85" s="10"/>
+    </row>
+    <row r="86" spans="1:7">
+      <c r="A86" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="B86" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="C86" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="D86" s="10"/>
+      <c r="E86" s="10"/>
+      <c r="F86" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="G86" s="10"/>
+    </row>
+    <row r="87" spans="1:7">
+      <c r="A87" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="B87" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="C87" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="D87" s="10"/>
+      <c r="E87" s="10"/>
+      <c r="F87" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="G87" s="10"/>
+    </row>
+    <row r="88" spans="1:7">
+      <c r="A88" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="B88" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="C88" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="D88" s="10"/>
+      <c r="E88" s="10"/>
+      <c r="F88" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="G88" s="10"/>
+    </row>
+    <row r="89" spans="1:7">
+      <c r="A89" s="10"/>
+      <c r="B89" s="10"/>
+      <c r="C89" s="11"/>
+      <c r="D89" s="10"/>
+      <c r="E89" s="10"/>
+      <c r="F89" s="10"/>
+      <c r="G89" s="10"/>
+    </row>
+    <row r="90" spans="1:7">
+      <c r="A90" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="B90" s="10">
+        <v>101</v>
+      </c>
+      <c r="C90" s="11">
+        <v>101</v>
+      </c>
+      <c r="D90" s="10"/>
+      <c r="E90" s="10"/>
+      <c r="F90" s="10"/>
+      <c r="G90" s="10" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7">
+      <c r="A91" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="B91" s="10">
+        <v>102</v>
+      </c>
+      <c r="C91" s="11">
+        <v>102</v>
+      </c>
+      <c r="D91" s="10"/>
+      <c r="E91" s="10"/>
+      <c r="F91" s="10"/>
+      <c r="G91" s="10" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7">
+      <c r="A92" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="B92" s="10">
+        <v>103</v>
+      </c>
+      <c r="C92" s="11">
+        <v>103</v>
+      </c>
+      <c r="D92" s="10"/>
+      <c r="E92" s="10"/>
+      <c r="F92" s="10"/>
+      <c r="G92" s="10" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7">
+      <c r="A93" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="B93" s="10">
+        <v>104</v>
+      </c>
+      <c r="C93" s="11">
+        <v>104</v>
+      </c>
+      <c r="D93" s="10"/>
+      <c r="E93" s="10"/>
+      <c r="F93" s="10"/>
+      <c r="G93" s="10" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7">
+      <c r="A94" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="B94" s="10">
+        <v>105</v>
+      </c>
+      <c r="C94" s="11">
+        <v>105</v>
+      </c>
+      <c r="D94" s="10"/>
+      <c r="E94" s="10"/>
+      <c r="F94" s="10"/>
+      <c r="G94" s="10" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7">
+      <c r="A95" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="B95" s="10">
+        <v>106</v>
+      </c>
+      <c r="C95" s="11">
+        <v>106</v>
+      </c>
+      <c r="D95" s="10"/>
+      <c r="E95" s="10"/>
+      <c r="F95" s="10"/>
+      <c r="G95" s="10" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7">
+      <c r="A96" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="B96" s="10">
+        <v>107</v>
+      </c>
+      <c r="C96" s="11">
+        <v>107</v>
+      </c>
+      <c r="D96" s="10"/>
+      <c r="E96" s="10"/>
+      <c r="F96" s="10"/>
+      <c r="G96" s="10" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7">
+      <c r="A97" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="B97" s="10">
+        <v>108</v>
+      </c>
+      <c r="C97" s="11">
+        <v>108</v>
+      </c>
+      <c r="D97" s="10"/>
+      <c r="E97" s="10"/>
+      <c r="F97" s="10"/>
+      <c r="G97" s="10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7">
+      <c r="A98" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="B98" s="10">
+        <v>109</v>
+      </c>
+      <c r="C98" s="11">
+        <v>109</v>
+      </c>
+      <c r="D98" s="10"/>
+      <c r="E98" s="10"/>
+      <c r="F98" s="10"/>
+      <c r="G98" s="10" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7">
+      <c r="A99" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="B99" s="10">
+        <v>110</v>
+      </c>
+      <c r="C99" s="11">
+        <v>110</v>
+      </c>
+      <c r="D99" s="10"/>
+      <c r="E99" s="10"/>
+      <c r="F99" s="10"/>
+      <c r="G99" s="10" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7">
+      <c r="A100" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="B100" s="10">
+        <v>111</v>
+      </c>
+      <c r="C100" s="11">
+        <v>111</v>
+      </c>
+      <c r="D100" s="10"/>
+      <c r="E100" s="10"/>
+      <c r="F100" s="10"/>
+      <c r="G100" s="10" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7">
+      <c r="A101" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="B101" s="10">
+        <v>112</v>
+      </c>
+      <c r="C101" s="11">
+        <v>112</v>
+      </c>
+      <c r="D101" s="10"/>
+      <c r="E101" s="10"/>
+      <c r="F101" s="10"/>
+      <c r="G101" s="10" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7">
+      <c r="A102" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="B102" s="10">
+        <v>113</v>
+      </c>
+      <c r="C102" s="11">
+        <v>113</v>
+      </c>
+      <c r="D102" s="10"/>
+      <c r="E102" s="10"/>
+      <c r="F102" s="10"/>
+      <c r="G102" s="10" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7">
+      <c r="A103" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="B103" s="10">
+        <v>114</v>
+      </c>
+      <c r="C103" s="11">
+        <v>114</v>
+      </c>
+      <c r="D103" s="10"/>
+      <c r="E103" s="10"/>
+      <c r="F103" s="10"/>
+      <c r="G103" s="10" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7">
+      <c r="A104" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="B104" s="10">
+        <v>115</v>
+      </c>
+      <c r="C104" s="11">
+        <v>115</v>
+      </c>
+      <c r="D104" s="10"/>
+      <c r="E104" s="10"/>
+      <c r="F104" s="10"/>
+      <c r="G104" s="10" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7">
+      <c r="A105" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="B105" s="10">
+        <v>116</v>
+      </c>
+      <c r="C105" s="11">
+        <v>116</v>
+      </c>
+      <c r="D105" s="10"/>
+      <c r="E105" s="10"/>
+      <c r="F105" s="10"/>
+      <c r="G105" s="10" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7">
+      <c r="A106" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="B106" s="10">
+        <v>117</v>
+      </c>
+      <c r="C106" s="11">
+        <v>117</v>
+      </c>
+      <c r="D106" s="10"/>
+      <c r="E106" s="10"/>
+      <c r="F106" s="10"/>
+      <c r="G106" s="10" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7">
+      <c r="A107" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="B107" s="10">
+        <v>118</v>
+      </c>
+      <c r="C107" s="11">
+        <v>118</v>
+      </c>
+      <c r="D107" s="10"/>
+      <c r="E107" s="10"/>
+      <c r="F107" s="10"/>
+      <c r="G107" s="10" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7">
+      <c r="A108" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="B108" s="10">
+        <v>119</v>
+      </c>
+      <c r="C108" s="11">
+        <v>119</v>
+      </c>
+      <c r="D108" s="10"/>
+      <c r="E108" s="10"/>
+      <c r="F108" s="10"/>
+      <c r="G108" s="10" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7">
+      <c r="A109" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="B109" s="10">
+        <v>120</v>
+      </c>
+      <c r="C109" s="11">
+        <v>120</v>
+      </c>
+      <c r="D109" s="10"/>
+      <c r="E109" s="10"/>
+      <c r="F109" s="10"/>
+      <c r="G109" s="10" t="s">
+        <v>128</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1678,7 +3392,7 @@
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="44.125" customWidth="1"/>
-    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="3" width="15.875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="22.125" bestFit="1" customWidth="1"/>
   </cols>
@@ -1699,10 +3413,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>29</v>
+        <v>153</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>28</v>
+        <v>154</v>
       </c>
       <c r="C2" t="s">
         <v>20</v>

--- a/Demo/MDA/demo_mda_9999_1_location.xlsx
+++ b/Demo/MDA/demo_mda_9999_1_location.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\Demo\MDA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bonhe\Repositories\dsa-forms\Demo\MDA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E120B472-3A85-4198-A4FD-B1CB12F32477}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92CCE308-89F7-4F6A-99F1-35A4720D47B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="176">
   <si>
     <t>type</t>
   </si>
@@ -496,12 +496,6 @@
     <t>${l_eligible_boy_0_4} + ${l_eligible_girl_0_4} + ${l_eligible_boy_5_14} + ${l_eligible_girl_5_14} + ${l_eligible_boy_15_more} + ${l_eligible_girl_15_more}</t>
   </si>
   <si>
-    <t>(Demo) 1. MDA Location Form V2</t>
-  </si>
-  <si>
-    <t>demo_mda_9999_1_location_v2</t>
-  </si>
-  <si>
     <t>l_recorder_id</t>
   </si>
   <si>
@@ -548,6 +542,27 @@
   </si>
   <si>
     <t>Select the recorder ID</t>
+  </si>
+  <si>
+    <t>${l_state}</t>
+  </si>
+  <si>
+    <t>demo_mda_9999_1_location_v2_1</t>
+  </si>
+  <si>
+    <t>(Demo) 1. MDA Location Form V2.1</t>
+  </si>
+  <si>
+    <t>${l_district}</t>
+  </si>
+  <si>
+    <t>${l_health_facility}</t>
+  </si>
+  <si>
+    <t>bind::db_add_col_5</t>
+  </si>
+  <si>
+    <t>${l_location}</t>
   </si>
 </sst>
 </file>
@@ -992,7 +1007,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:R20"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="28" style="4" bestFit="1" customWidth="1"/>
@@ -1012,10 +1027,11 @@
     <col min="15" max="15" width="18" style="4" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="20.875" style="4" customWidth="1"/>
     <col min="17" max="17" width="20.375" style="4" customWidth="1"/>
-    <col min="18" max="16384" width="11" style="4"/>
+    <col min="18" max="18" width="18" style="4" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="11" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1">
+    <row r="1" spans="1:18" s="1" customFormat="1">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1067,16 +1083,19 @@
       <c r="Q1" s="21" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" s="3" customFormat="1">
+      <c r="R1" s="21" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" s="3" customFormat="1">
       <c r="A2" s="15" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C2" s="22" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D2" s="22"/>
       <c r="E2" s="15"/>
@@ -1092,8 +1111,9 @@
       <c r="O2" s="23"/>
       <c r="P2" s="23"/>
       <c r="Q2" s="23"/>
-    </row>
-    <row r="3" spans="1:17" ht="26.25">
+      <c r="R2" s="16"/>
+    </row>
+    <row r="3" spans="1:18" ht="26.25">
       <c r="A3" s="9" t="s">
         <v>36</v>
       </c>
@@ -1121,8 +1141,9 @@
       <c r="O3" s="9"/>
       <c r="P3" s="9"/>
       <c r="Q3" s="9"/>
-    </row>
-    <row r="4" spans="1:17" ht="26.25">
+      <c r="R3" s="9"/>
+    </row>
+    <row r="4" spans="1:18" ht="26.25">
       <c r="A4" s="9" t="s">
         <v>37</v>
       </c>
@@ -1146,14 +1167,17 @@
         <v>40</v>
       </c>
       <c r="M4" s="9"/>
-      <c r="N4" s="9"/>
+      <c r="N4" s="9" t="s">
+        <v>169</v>
+      </c>
       <c r="O4" s="13" t="s">
         <v>25</v>
       </c>
       <c r="P4" s="9"/>
       <c r="Q4" s="9"/>
-    </row>
-    <row r="5" spans="1:17" ht="26.25">
+      <c r="R4" s="9"/>
+    </row>
+    <row r="5" spans="1:18" ht="26.25">
       <c r="A5" s="9" t="s">
         <v>131</v>
       </c>
@@ -1178,11 +1202,16 @@
       </c>
       <c r="M5" s="9"/>
       <c r="N5" s="9"/>
-      <c r="O5" s="9"/>
-      <c r="P5" s="13"/>
+      <c r="O5" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="P5" s="13" t="s">
+        <v>25</v>
+      </c>
       <c r="Q5" s="9"/>
-    </row>
-    <row r="6" spans="1:17" ht="33.75">
+      <c r="R5" s="9"/>
+    </row>
+    <row r="6" spans="1:18" ht="33.75">
       <c r="A6" s="9" t="s">
         <v>132</v>
       </c>
@@ -1208,12 +1237,15 @@
       <c r="M6" s="9"/>
       <c r="N6" s="9"/>
       <c r="O6" s="9"/>
-      <c r="P6" s="13" t="s">
+      <c r="P6" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="Q6" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="Q6" s="9"/>
-    </row>
-    <row r="7" spans="1:17" ht="26.25">
+      <c r="R6" s="9"/>
+    </row>
+    <row r="7" spans="1:18" ht="26.25">
       <c r="A7" s="9" t="s">
         <v>133</v>
       </c>
@@ -1240,11 +1272,14 @@
       <c r="N7" s="9"/>
       <c r="O7" s="9"/>
       <c r="P7" s="9"/>
-      <c r="Q7" s="13" t="s">
+      <c r="Q7" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="R7" s="13" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:18">
       <c r="A8" s="9" t="s">
         <v>47</v>
       </c>
@@ -1270,8 +1305,9 @@
       <c r="O8" s="9"/>
       <c r="P8" s="9"/>
       <c r="Q8" s="9"/>
-    </row>
-    <row r="9" spans="1:17">
+      <c r="R8" s="9"/>
+    </row>
+    <row r="9" spans="1:18">
       <c r="A9" s="9" t="s">
         <v>47</v>
       </c>
@@ -1297,8 +1333,9 @@
       <c r="O9" s="9"/>
       <c r="P9" s="9"/>
       <c r="Q9" s="9"/>
-    </row>
-    <row r="10" spans="1:17">
+      <c r="R9" s="9"/>
+    </row>
+    <row r="10" spans="1:18">
       <c r="A10" s="9" t="s">
         <v>47</v>
       </c>
@@ -1324,8 +1361,9 @@
       <c r="O10" s="9"/>
       <c r="P10" s="9"/>
       <c r="Q10" s="9"/>
-    </row>
-    <row r="11" spans="1:17">
+      <c r="R10" s="9"/>
+    </row>
+    <row r="11" spans="1:18">
       <c r="A11" s="9" t="s">
         <v>47</v>
       </c>
@@ -1351,8 +1389,9 @@
       <c r="O11" s="9"/>
       <c r="P11" s="9"/>
       <c r="Q11" s="9"/>
-    </row>
-    <row r="12" spans="1:17">
+      <c r="R11" s="9"/>
+    </row>
+    <row r="12" spans="1:18">
       <c r="A12" s="9" t="s">
         <v>47</v>
       </c>
@@ -1378,8 +1417,9 @@
       <c r="O12" s="9"/>
       <c r="P12" s="9"/>
       <c r="Q12" s="9"/>
-    </row>
-    <row r="13" spans="1:17">
+      <c r="R12" s="9"/>
+    </row>
+    <row r="13" spans="1:18">
       <c r="A13" s="9" t="s">
         <v>47</v>
       </c>
@@ -1405,8 +1445,9 @@
       <c r="O13" s="9"/>
       <c r="P13" s="9"/>
       <c r="Q13" s="9"/>
-    </row>
-    <row r="14" spans="1:17">
+      <c r="R13" s="9"/>
+    </row>
+    <row r="14" spans="1:18">
       <c r="A14" s="9" t="s">
         <v>47</v>
       </c>
@@ -1432,8 +1473,9 @@
       <c r="O14" s="9"/>
       <c r="P14" s="9"/>
       <c r="Q14" s="9"/>
-    </row>
-    <row r="15" spans="1:17">
+      <c r="R14" s="9"/>
+    </row>
+    <row r="15" spans="1:18">
       <c r="A15" s="9" t="s">
         <v>150</v>
       </c>
@@ -1459,8 +1501,9 @@
       <c r="O15" s="9"/>
       <c r="P15" s="9"/>
       <c r="Q15" s="9"/>
-    </row>
-    <row r="16" spans="1:17">
+      <c r="R15" s="9"/>
+    </row>
+    <row r="16" spans="1:18">
       <c r="A16" s="9" t="s">
         <v>14</v>
       </c>
@@ -1488,8 +1531,9 @@
       <c r="O16" s="9"/>
       <c r="P16" s="9"/>
       <c r="Q16" s="9"/>
-    </row>
-    <row r="17" spans="1:17">
+      <c r="R16" s="9"/>
+    </row>
+    <row r="17" spans="1:18">
       <c r="A17" s="9" t="s">
         <v>13</v>
       </c>
@@ -1515,8 +1559,9 @@
       <c r="O17" s="9"/>
       <c r="P17" s="9"/>
       <c r="Q17" s="9"/>
-    </row>
-    <row r="18" spans="1:17">
+      <c r="R17" s="9"/>
+    </row>
+    <row r="18" spans="1:18">
       <c r="A18" s="9" t="s">
         <v>15</v>
       </c>
@@ -1542,8 +1587,9 @@
       <c r="O18" s="9"/>
       <c r="P18" s="9"/>
       <c r="Q18" s="9"/>
-    </row>
-    <row r="19" spans="1:17">
+      <c r="R18" s="9"/>
+    </row>
+    <row r="19" spans="1:18">
       <c r="A19" s="9" t="s">
         <v>55</v>
       </c>
@@ -1565,8 +1611,9 @@
       <c r="O19" s="9"/>
       <c r="P19" s="9"/>
       <c r="Q19" s="9"/>
-    </row>
-    <row r="20" spans="1:17">
+      <c r="R19" s="9"/>
+    </row>
+    <row r="20" spans="1:18">
       <c r="A20" s="9" t="s">
         <v>56</v>
       </c>
@@ -1588,6 +1635,7 @@
       <c r="O20" s="9"/>
       <c r="P20" s="9"/>
       <c r="Q20" s="9"/>
+      <c r="R20" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1632,13 +1680,13 @@
     </row>
     <row r="2" spans="1:7" s="4" customFormat="1">
       <c r="A2" s="16" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9"/>
@@ -1647,13 +1695,13 @@
     </row>
     <row r="3" spans="1:7" s="4" customFormat="1">
       <c r="A3" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="B3" s="18" t="s">
         <v>156</v>
       </c>
-      <c r="B3" s="18" t="s">
-        <v>158</v>
-      </c>
       <c r="C3" s="19" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
@@ -1662,13 +1710,13 @@
     </row>
     <row r="4" spans="1:7" s="4" customFormat="1">
       <c r="A4" s="16" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -1677,13 +1725,13 @@
     </row>
     <row r="5" spans="1:7" s="4" customFormat="1">
       <c r="A5" s="16" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
@@ -1692,13 +1740,13 @@
     </row>
     <row r="6" spans="1:7" s="4" customFormat="1">
       <c r="A6" s="16" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="9"/>
@@ -1707,13 +1755,13 @@
     </row>
     <row r="7" spans="1:7" s="4" customFormat="1">
       <c r="A7" s="16" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
@@ -1722,13 +1770,13 @@
     </row>
     <row r="8" spans="1:7" s="4" customFormat="1">
       <c r="A8" s="16" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
@@ -1737,13 +1785,13 @@
     </row>
     <row r="9" spans="1:7" s="4" customFormat="1">
       <c r="A9" s="16" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
@@ -1752,13 +1800,13 @@
     </row>
     <row r="10" spans="1:7" s="4" customFormat="1">
       <c r="A10" s="16" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
@@ -1767,13 +1815,13 @@
     </row>
     <row r="11" spans="1:7" s="4" customFormat="1">
       <c r="A11" s="16" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
@@ -1782,13 +1830,13 @@
     </row>
     <row r="12" spans="1:7" s="4" customFormat="1">
       <c r="A12" s="16" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
@@ -1797,13 +1845,13 @@
     </row>
     <row r="13" spans="1:7" s="4" customFormat="1">
       <c r="A13" s="16" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
@@ -1812,7 +1860,7 @@
     </row>
     <row r="14" spans="1:7" s="4" customFormat="1">
       <c r="A14" s="16" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B14" s="16">
         <v>99</v>
@@ -3413,10 +3461,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="C2" t="s">
         <v>20</v>

--- a/Demo/MDA/demo_mda_9999_1_location.xlsx
+++ b/Demo/MDA/demo_mda_9999_1_location.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bonhe\Repositories\dsa-forms\Demo\MDA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\Demo\MDA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92CCE308-89F7-4F6A-99F1-35A4720D47B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5095D79-9101-4365-8B77-CB5ADF125D38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="170">
   <si>
     <t>type</t>
   </si>
@@ -451,51 +451,12 @@
     <t>location = ${l_location}</t>
   </si>
   <si>
-    <t>Total number of boys aged 0-4 years eligible for treatment</t>
-  </si>
-  <si>
-    <t>Total number of girls aged 0-4 years eligible for treatment</t>
-  </si>
-  <si>
-    <t>Total number of boys aged 5-14 years eligible for treatment</t>
-  </si>
-  <si>
-    <t>Total number of girls aged 5-14 years eligible for treatment</t>
-  </si>
-  <si>
-    <t>Total number of boys aged more than 15 years eligible for treatment</t>
-  </si>
-  <si>
-    <t>Total number of girls aged more than years eligible for treatment</t>
-  </si>
-  <si>
-    <t>l_eligible_boy_0_4</t>
-  </si>
-  <si>
-    <t>l_eligible_boy_5_14</t>
-  </si>
-  <si>
-    <t>l_eligible_girl_0_4</t>
-  </si>
-  <si>
-    <t>l_eligible_girl_5_14</t>
-  </si>
-  <si>
-    <t>l_eligible_boy_15_more</t>
-  </si>
-  <si>
-    <t>l_eligible_girl_15_more</t>
-  </si>
-  <si>
     <t>calculate</t>
   </si>
   <si>
     <t>Total eligible population of the village</t>
   </si>
   <si>
-    <t>${l_eligible_boy_0_4} + ${l_eligible_girl_0_4} + ${l_eligible_boy_5_14} + ${l_eligible_girl_5_14} + ${l_eligible_boy_15_more} + ${l_eligible_girl_15_more}</t>
-  </si>
-  <si>
     <t>l_recorder_id</t>
   </si>
   <si>
@@ -547,12 +508,6 @@
     <t>${l_state}</t>
   </si>
   <si>
-    <t>demo_mda_9999_1_location_v2_1</t>
-  </si>
-  <si>
-    <t>(Demo) 1. MDA Location Form V2.1</t>
-  </si>
-  <si>
     <t>${l_district}</t>
   </si>
   <si>
@@ -563,13 +518,40 @@
   </si>
   <si>
     <t>${l_location}</t>
+  </si>
+  <si>
+    <t>Total number of people aged 15 years and above in the village</t>
+  </si>
+  <si>
+    <t>Total number of people aged 5-14 years of the Village</t>
+  </si>
+  <si>
+    <t>Total number of people aged 1-4 years of the village</t>
+  </si>
+  <si>
+    <t>I_total_popn_1_4</t>
+  </si>
+  <si>
+    <t>I_total_popn_5_14</t>
+  </si>
+  <si>
+    <t>I_total_popn_15_More</t>
+  </si>
+  <si>
+    <t>${I_total_popn_1_4} + ${I_total_popn_5_14} + ${I_total_popn_15_More}</t>
+  </si>
+  <si>
+    <t>(Demo) 1. MDA Location Form V3</t>
+  </si>
+  <si>
+    <t>demo_mda_9999_1_location_v3</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -627,6 +609,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -670,7 +659,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -725,6 +714,9 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1007,7 +999,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R20"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="28" style="4" bestFit="1" customWidth="1"/>
@@ -1084,18 +1076,18 @@
         <v>24</v>
       </c>
       <c r="R1" s="21" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
     </row>
     <row r="2" spans="1:18" s="3" customFormat="1">
       <c r="A2" s="15" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="C2" s="22" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="D2" s="22"/>
       <c r="E2" s="15"/>
@@ -1168,7 +1160,7 @@
       </c>
       <c r="M4" s="9"/>
       <c r="N4" s="9" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="O4" s="13" t="s">
         <v>25</v>
@@ -1203,7 +1195,7 @@
       <c r="M5" s="9"/>
       <c r="N5" s="9"/>
       <c r="O5" s="9" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="P5" s="13" t="s">
         <v>25</v>
@@ -1238,7 +1230,7 @@
       <c r="N6" s="9"/>
       <c r="O6" s="9"/>
       <c r="P6" s="9" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="Q6" s="13" t="s">
         <v>25</v>
@@ -1273,7 +1265,7 @@
       <c r="O7" s="9"/>
       <c r="P7" s="9"/>
       <c r="Q7" s="9" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="R7" s="13" t="s">
         <v>25</v>
@@ -1307,109 +1299,109 @@
       <c r="Q8" s="9"/>
       <c r="R8" s="9"/>
     </row>
-    <row r="9" spans="1:18">
-      <c r="A9" s="9" t="s">
+    <row r="9" spans="1:18" s="26" customFormat="1">
+      <c r="A9" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="B9" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="D9" s="12"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9" t="s">
+      <c r="B9" s="25" t="s">
+        <v>164</v>
+      </c>
+      <c r="C9" s="24" t="s">
+        <v>163</v>
+      </c>
+      <c r="D9" s="24"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="24"/>
+      <c r="H9" s="25"/>
+      <c r="I9" s="25"/>
+      <c r="J9" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="K9" s="9"/>
-      <c r="L9" s="9"/>
-      <c r="M9" s="9"/>
-      <c r="N9" s="9"/>
-      <c r="O9" s="9"/>
-      <c r="P9" s="9"/>
-      <c r="Q9" s="9"/>
-      <c r="R9" s="9"/>
-    </row>
-    <row r="10" spans="1:18">
-      <c r="A10" s="9" t="s">
+      <c r="K9" s="25"/>
+      <c r="L9" s="25"/>
+      <c r="M9" s="25"/>
+      <c r="N9" s="25"/>
+      <c r="O9" s="25"/>
+      <c r="P9" s="25"/>
+      <c r="Q9" s="25"/>
+      <c r="R9" s="25"/>
+    </row>
+    <row r="10" spans="1:18" s="26" customFormat="1">
+      <c r="A10" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="B10" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>139</v>
-      </c>
-      <c r="D10" s="12"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9" t="s">
+      <c r="B10" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>162</v>
+      </c>
+      <c r="D10" s="24"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="25"/>
+      <c r="G10" s="24"/>
+      <c r="H10" s="25"/>
+      <c r="I10" s="25"/>
+      <c r="J10" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="K10" s="9"/>
-      <c r="L10" s="9"/>
-      <c r="M10" s="9"/>
-      <c r="N10" s="9"/>
-      <c r="O10" s="9"/>
-      <c r="P10" s="9"/>
-      <c r="Q10" s="9"/>
-      <c r="R10" s="9"/>
-    </row>
-    <row r="11" spans="1:18">
-      <c r="A11" s="9" t="s">
+      <c r="K10" s="25"/>
+      <c r="L10" s="25"/>
+      <c r="M10" s="25"/>
+      <c r="N10" s="25"/>
+      <c r="O10" s="25"/>
+      <c r="P10" s="25"/>
+      <c r="Q10" s="25"/>
+      <c r="R10" s="25"/>
+    </row>
+    <row r="11" spans="1:18" s="26" customFormat="1">
+      <c r="A11" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="D11" s="12"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9" t="s">
+      <c r="B11" s="25" t="s">
+        <v>166</v>
+      </c>
+      <c r="C11" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="D11" s="24"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="25"/>
+      <c r="I11" s="25"/>
+      <c r="J11" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="K11" s="9"/>
-      <c r="L11" s="9"/>
-      <c r="M11" s="9"/>
-      <c r="N11" s="9"/>
-      <c r="O11" s="9"/>
-      <c r="P11" s="9"/>
-      <c r="Q11" s="9"/>
-      <c r="R11" s="9"/>
+      <c r="K11" s="25"/>
+      <c r="L11" s="25"/>
+      <c r="M11" s="25"/>
+      <c r="N11" s="25"/>
+      <c r="O11" s="25"/>
+      <c r="P11" s="25"/>
+      <c r="Q11" s="25"/>
+      <c r="R11" s="25"/>
     </row>
     <row r="12" spans="1:18">
       <c r="A12" s="9" t="s">
-        <v>47</v>
+        <v>138</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>147</v>
+        <v>49</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D12" s="12"/>
       <c r="E12" s="9"/>
       <c r="F12" s="9"/>
       <c r="G12" s="12"/>
       <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9" t="s">
-        <v>12</v>
-      </c>
+      <c r="I12" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="J12" s="9"/>
       <c r="K12" s="9"/>
       <c r="L12" s="9"/>
       <c r="M12" s="9"/>
@@ -1421,16 +1413,18 @@
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="9" t="s">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>148</v>
+        <v>50</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>142</v>
+        <v>29</v>
       </c>
       <c r="D13" s="12"/>
-      <c r="E13" s="9"/>
+      <c r="E13" s="9" t="s">
+        <v>51</v>
+      </c>
       <c r="F13" s="9"/>
       <c r="G13" s="12"/>
       <c r="H13" s="9"/>
@@ -1449,13 +1443,13 @@
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="9" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>149</v>
+        <v>52</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>143</v>
+        <v>30</v>
       </c>
       <c r="D14" s="12"/>
       <c r="E14" s="9"/>
@@ -1477,23 +1471,23 @@
     </row>
     <row r="15" spans="1:18">
       <c r="A15" s="9" t="s">
-        <v>150</v>
+        <v>15</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>151</v>
+        <v>31</v>
       </c>
       <c r="D15" s="12"/>
       <c r="E15" s="9"/>
       <c r="F15" s="9"/>
       <c r="G15" s="12"/>
       <c r="H15" s="9"/>
-      <c r="I15" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="J15" s="9"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="9" t="s">
+        <v>54</v>
+      </c>
       <c r="K15" s="9"/>
       <c r="L15" s="9"/>
       <c r="M15" s="9"/>
@@ -1505,25 +1499,19 @@
     </row>
     <row r="16" spans="1:18">
       <c r="A16" s="9" t="s">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>29</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="C16" s="12"/>
       <c r="D16" s="12"/>
-      <c r="E16" s="9" t="s">
-        <v>51</v>
-      </c>
+      <c r="E16" s="9"/>
       <c r="F16" s="9"/>
       <c r="G16" s="12"/>
       <c r="H16" s="9"/>
       <c r="I16" s="9"/>
-      <c r="J16" s="9" t="s">
-        <v>12</v>
-      </c>
+      <c r="J16" s="9"/>
       <c r="K16" s="9"/>
       <c r="L16" s="9"/>
       <c r="M16" s="9"/>
@@ -1535,23 +1523,19 @@
     </row>
     <row r="17" spans="1:18">
       <c r="A17" s="9" t="s">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>30</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="C17" s="12"/>
       <c r="D17" s="12"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9"/>
       <c r="G17" s="12"/>
       <c r="H17" s="9"/>
       <c r="I17" s="9"/>
-      <c r="J17" s="9" t="s">
-        <v>12</v>
-      </c>
+      <c r="J17" s="9"/>
       <c r="K17" s="9"/>
       <c r="L17" s="9"/>
       <c r="M17" s="9"/>
@@ -1561,83 +1545,8 @@
       <c r="Q17" s="9"/>
       <c r="R17" s="9"/>
     </row>
-    <row r="18" spans="1:18">
-      <c r="A18" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="D18" s="12"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="K18" s="9"/>
-      <c r="L18" s="9"/>
-      <c r="M18" s="9"/>
-      <c r="N18" s="9"/>
-      <c r="O18" s="9"/>
-      <c r="P18" s="9"/>
-      <c r="Q18" s="9"/>
-      <c r="R18" s="9"/>
-    </row>
-    <row r="19" spans="1:18">
-      <c r="A19" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="9"/>
-      <c r="K19" s="9"/>
-      <c r="L19" s="9"/>
-      <c r="M19" s="9"/>
-      <c r="N19" s="9"/>
-      <c r="O19" s="9"/>
-      <c r="P19" s="9"/>
-      <c r="Q19" s="9"/>
-      <c r="R19" s="9"/>
-    </row>
-    <row r="20" spans="1:18">
-      <c r="A20" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="12"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
-      <c r="K20" s="9"/>
-      <c r="L20" s="9"/>
-      <c r="M20" s="9"/>
-      <c r="N20" s="9"/>
-      <c r="O20" s="9"/>
-      <c r="P20" s="9"/>
-      <c r="Q20" s="9"/>
-      <c r="R20" s="9"/>
-    </row>
   </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -1680,13 +1589,13 @@
     </row>
     <row r="2" spans="1:7" s="4" customFormat="1">
       <c r="A2" s="16" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9"/>
@@ -1695,13 +1604,13 @@
     </row>
     <row r="3" spans="1:7" s="4" customFormat="1">
       <c r="A3" s="16" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
@@ -1710,13 +1619,13 @@
     </row>
     <row r="4" spans="1:7" s="4" customFormat="1">
       <c r="A4" s="16" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -1725,13 +1634,13 @@
     </row>
     <row r="5" spans="1:7" s="4" customFormat="1">
       <c r="A5" s="16" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
@@ -1740,13 +1649,13 @@
     </row>
     <row r="6" spans="1:7" s="4" customFormat="1">
       <c r="A6" s="16" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="9"/>
@@ -1755,13 +1664,13 @@
     </row>
     <row r="7" spans="1:7" s="4" customFormat="1">
       <c r="A7" s="16" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
@@ -1770,13 +1679,13 @@
     </row>
     <row r="8" spans="1:7" s="4" customFormat="1">
       <c r="A8" s="16" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
@@ -1785,13 +1694,13 @@
     </row>
     <row r="9" spans="1:7" s="4" customFormat="1">
       <c r="A9" s="16" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
@@ -1800,13 +1709,13 @@
     </row>
     <row r="10" spans="1:7" s="4" customFormat="1">
       <c r="A10" s="16" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
@@ -1815,13 +1724,13 @@
     </row>
     <row r="11" spans="1:7" s="4" customFormat="1">
       <c r="A11" s="16" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
@@ -1830,13 +1739,13 @@
     </row>
     <row r="12" spans="1:7" s="4" customFormat="1">
       <c r="A12" s="16" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
@@ -1845,13 +1754,13 @@
     </row>
     <row r="13" spans="1:7" s="4" customFormat="1">
       <c r="A13" s="16" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
@@ -1860,7 +1769,7 @@
     </row>
     <row r="14" spans="1:7" s="4" customFormat="1">
       <c r="A14" s="16" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="B14" s="16">
         <v>99</v>
@@ -3461,10 +3370,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C2" t="s">
         <v>20</v>

--- a/Demo/MDA/demo_mda_9999_1_location.xlsx
+++ b/Demo/MDA/demo_mda_9999_1_location.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\Demo\MDA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5095D79-9101-4365-8B77-CB5ADF125D38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AA73ED3-59E7-42DD-AC8C-A219E64B33DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
